--- a/BdsL_paper_Summary.xlsx
+++ b/BdsL_paper_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BDSL_CapstonProject_\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4957EEEB-AA9B-4D74-A382-FF66A99338E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B4A360-2FE8-44D4-9A6D-8B310E5DB656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B9C80F48-A763-4B93-A58D-04AE71AFC590}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B9C80F48-A763-4B93-A58D-04AE71AFC590}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Paper Title</t>
   </si>
@@ -54,13 +54,154 @@
   </si>
   <si>
     <t>Result</t>
+  </si>
+  <si>
+    <t>BAUST Lipi: A BdSL Dataset with Deep Learning Based Bangla Sign Language Recognition</t>
+  </si>
+  <si>
+    <t>Created a new, comprehensive BdSL dataset (BAUST Lipi) and devised a hybrid CNN-LSTM model to solve the problem of achieving high-performance accuracy in BdSL recognition</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BDSL 49: A comprehensive dataset of Bangla sign language</t>
+  </si>
+  <si>
+    <t>BDSL 49, consisting of 29,490 images across 49 classes of Bengali alphabets, numeric characters, and special characters</t>
+  </si>
+  <si>
+    <t>Provided a freely available, comprehensive 49-class dataset to enable researchers to train and evaluate machine learning models specifically for Bengali Sign Language</t>
+  </si>
+  <si>
+    <t>The YOLOv4 model achieved 99.4% accuracy (99.9% mean average precision) for detection, and the Xception model achieved the highest recognition accuracy at 93%</t>
+  </si>
+  <si>
+    <t>BdSLW60: A Word-Level Bangla Sign Language Dataset</t>
+  </si>
+  <si>
+    <t>BdSLW60, a word-level dataset containing 9,307 video trials of 60 Bengali sign words performed by 18 signers in an unconstrained setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Extracted landmark-based features (pose, face, and hands) using Google MediaPipe, and applied a unique relative quantization-based key frame encoding technique. Evaluated using SVM, SVM-DTW, and an attention-based bi-LSTM network</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Addressed the scarcity of word-level BdSL datasets by creating BdSLW60 and proposed a novel relative quantization approach for continuous sign language recognition</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Benchmarking showed a testing accuracy of up to 67.6% using SVM and up to 75.1% using the attention-based bi-LSTM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bilingual Sign Language Recognition: A YOLOv11-Based Model for Bangla and English Alphabets</t>
+  </si>
+  <si>
+    <t>A custom open-source dataset of 9,556 images representing 64 distinct letter signs from both Bangla Sign Language (BdSL) and American Sign Language (ASL)</t>
+  </si>
+  <si>
+    <t>Utilized the state-of-the-art YOLOv11 object detection architecture for real-time recognition. Data augmentation (cropping, rotation, brightness correction) was applied to enhance generalizability</t>
+  </si>
+  <si>
+    <t>Introduced a unified bilingual detection system capable of recognizing both BdSL and ASL alphabets concurrently in real-time to enhance interlingual communication</t>
+  </si>
+  <si>
+    <t>Dynamic BDSL Digit Recognition Using Hybrid 3DCNN+BiLSTM Model</t>
+  </si>
+  <si>
+    <t>Not explicitly stated (recent based on context).</t>
+  </si>
+  <si>
+    <t>A subset of the SignBD-Word dataset utilizing 11 numeral Bengali digit signs composed of extracted RGB human body pose keypoints skeleton data</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A hybrid architecture combining 3DCNN and bidirectional LSTM (BiLSTM) layers, utilizing DenseNet-201 as a base feature extractor for classifying body joint skeleton motion patterns</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The ensemble model (DenseNet-201+3DCNN+BiLSTM) achieved the highest scores (Precision 0.37, Recall 0.36, F1-Score 0.33), which increased accuracy by 4.54% compared to using DenseNet-201+BiLSTM alone</t>
+  </si>
+  <si>
+    <t>Pioneered the implementation of DenseNet-201 combined with 3DCNN and BiLSTM for dynamic BdSL digit recognition based on skeleton motion patterns</t>
+  </si>
+  <si>
+    <t>IsharaNet: A robust nested feature fusion coupled with attention incorporated width scaled lightweight architecture for Bengali sign language recognition</t>
+  </si>
+  <si>
+    <t>Evaluated across four datasets: BdSL47, BdSLW-11, Shongket, and KU-BdSL</t>
+  </si>
+  <si>
+    <t>Proposed IsharaNet, a lightweight deep neural network architecture leveraging parallel convolutional operations, nested feature fusion, and spatial/channel attention mechanisms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Introduced a highly efficient, width-scaled lightweight architecture capable of accurately capturing complex gesture semantics across Bengali sign alphabets, numerals, and words</t>
+  </si>
+  <si>
+    <t>Achieved top accuracies of 99.85% for numerals, 99.77% for alphabets, and 99.09% for words, with a consistent AUC score of 0.999 across tasks, outperforming state-of-the-art models</t>
+  </si>
+  <si>
+    <t>KU-BdSL: An open dataset for Bengali sign language recognition</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KU-BdSL, consisting of 1,500 images categorized into 30 classes representing 38 Bengali consonants captured by 39 participants</t>
+  </si>
+  <si>
+    <t>Dataset creation and formatting. Images were captured using smartphone cameras under various lighting conditions and backgrounds. The dataset was structured into Uni-scale (USLD), Multi-scale (MSLD), and Annotated (AMSLD) formats utilizing DarkNet annotations</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Provided a reliable, well-structured, and open dataset focused on static single-hand gestures of Bengali consonants to facilitate the development of machine translation solutions</t>
+  </si>
+  <si>
+    <t>Successfully published the annotated dataset for public research use, paving the way for image or video-based consonant identification</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Recognition of Bangladeshi Sign Language (BdSL) Words using Deep Convolutional Neural Networks (DCNNs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A custom dataset of 992 images representing 10 frequently used BdSL words created by the authors</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Image preprocessing (rescaling, flipping, shearing) combined with training deep learning/transfer learning models including a modified CNN, DenseNet201, ResNet50-V2, and MobileNet-V2</t>
+  </si>
+  <si>
+    <t>Focused specifically on real-time BdSL word detection (rather than just characters or digits) to bridge the communication gap for the deaf and dumb community</t>
+  </si>
+  <si>
+    <t>DenseNet201 and ResNet50-V2 both achieved testing accuracies of 93%, outperforming the custom CNN (76%) and MobileNet-V2 (87%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Transformer based sign-to-text translation for Bangladeshi sign language</t>
+  </si>
+  <si>
+    <t>A custom dataset of 102 common BdSL words, converted into 91,800 landmark sequences (30 frames per video)</t>
+  </si>
+  <si>
+    <t>A feature-first pipeline using Google MediaPipe to extract 258 skeletal landmarks (hands and upper body) per frame. These sequences were classified using a lightweight Transformer encoder leveraging positional information and self-attention</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Standardized a reproducible, privacy-friendly data curation pipeline and introduced a compact, real-time Transformer model capable of modeling temporal structure directly over skeletal landmarks for 102 BdSL words</t>
+  </si>
+  <si>
+    <t>The Transformer model achieved 98.12% test accuracy, significantly outperforming baselines such as Sequential LSTM (81.21%) and SSD MobileNet V2 (78.02%)</t>
+  </si>
+  <si>
+    <t>BAUST Lipi, comprising 18,000 images covering 36 Bengali symbols (30 consonants and 6 vowels)</t>
+  </si>
+  <si>
+    <t>A hybrid Convolutional Neural Network (CNN) model integrated with multiple convolutional layers, dropout techniques, and LSTM layers</t>
+  </si>
+  <si>
+    <t>The proposed hybrid CNN-LSTM model achieved a testing accuracy rate of 97.28% (97.92% overall accuracy)</t>
+  </si>
+  <si>
+    <t>The study utilized YOLOv4 for real-time hand sign detection from full-frame images and tested multiple pre-trained deep learning models (Xception, InceptionV3, InceptionResNetv2, ResNet50V2, DenseNet) for cropped image recognition</t>
+  </si>
+  <si>
+    <t>The YOLOv11 model outperformed previous YOLO versions (v8, v9, v10, v12), achieving a precision of 99.12%, recall of 99.63%, and mAP of 99.4%</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,19 +210,54 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="20"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF303030"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF303030"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -96,13 +272,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -438,36 +626,235 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91718BDA-A7AF-4253-B864-230AF643558B}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="44.81640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="48.08984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="41.26953125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="34.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.90625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="48.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="53.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="45" style="1" customWidth="1"/>
     <col min="7" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="26" x14ac:dyDescent="0.6">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" ht="20.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="99" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="99" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2025</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2025</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="62" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2025</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/BdsL_paper_Summary.xlsx
+++ b/BdsL_paper_Summary.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BDSL_CapstonProject_\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B4A360-2FE8-44D4-9A6D-8B310E5DB656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B9C80F48-A763-4B93-A58D-04AE71AFC590}"/>
+    <workbookView windowWidth="20490" windowHeight="6780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Paper Title</t>
   </si>
@@ -56,18 +47,48 @@
     <t>Result</t>
   </si>
   <si>
+    <t>KUNet-An Optimized AI Based Bengali Sign Language Translator for Hearing Impaired and Non Verbal People</t>
+  </si>
+  <si>
+    <t>KU-BdSL (Khulna University Bengali Sign Language Dataset)
+Variant Used: Uni-scale Sign Language Dataset (USLD)</t>
+  </si>
+  <si>
+    <t>KUNet (Khulna University Network), a CNN-based classification framework optimized with GA(Genetic-Algorithm) and XAI(explainable AI)(LIME)</t>
+  </si>
+  <si>
+    <t>Introduced KUNet, a novel GA-optimized CNN model for BdSL consonant recognition.
+Demonstrated that a shallow, optimized model can outperform deeper architectures like VGG16, VGG19, ResNet50, and AlexNet on the same dataset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best Accuracy Achieved: 99.78% on the KU-BdSL dataset using GA-optimized KUNet.
+</t>
+  </si>
+  <si>
     <t>BAUST Lipi: A BdSL Dataset with Deep Learning Based Bangla Sign Language Recognition</t>
   </si>
   <si>
+    <t>BAUST Lipi, comprising 18,000 images covering 36 Bengali symbols (30 consonants and 6 vowels)</t>
+  </si>
+  <si>
+    <t>A hybrid Convolutional Neural Network (CNN) model integrated with multiple convolutional layers, dropout techniques, and LSTM layers</t>
+  </si>
+  <si>
     <t>Created a new, comprehensive BdSL dataset (BAUST Lipi) and devised a hybrid CNN-LSTM model to solve the problem of achieving high-performance accuracy in BdSL recognition</t>
   </si>
   <si>
+    <t>The proposed hybrid CNN-LSTM model achieved a testing accuracy rate of 97.28% (97.92% overall accuracy)</t>
+  </si>
+  <si>
     <t xml:space="preserve"> BDSL 49: A comprehensive dataset of Bangla sign language</t>
   </si>
   <si>
     <t>BDSL 49, consisting of 29,490 images across 49 classes of Bengali alphabets, numeric characters, and special characters</t>
   </si>
   <si>
+    <t>The study utilized YOLOv4 for real-time hand sign detection from full-frame images and tested multiple pre-trained deep learning models (Xception, InceptionV3, InceptionResNetv2, ResNet50V2, DenseNet) for cropped image recognition</t>
+  </si>
+  <si>
     <t>Provided a freely available, comprehensive 49-class dataset to enable researchers to train and evaluate machine learning models specifically for Bengali Sign Language</t>
   </si>
   <si>
@@ -101,24 +122,27 @@
     <t>Introduced a unified bilingual detection system capable of recognizing both BdSL and ASL alphabets concurrently in real-time to enhance interlingual communication</t>
   </si>
   <si>
+    <t>The YOLOv11 model outperformed previous YOLO versions (v8, v9, v10, v12), achieving a precision of 99.12%, recall of 99.63%, and mAP of 99.4%</t>
+  </si>
+  <si>
     <t>Dynamic BDSL Digit Recognition Using Hybrid 3DCNN+BiLSTM Model</t>
   </si>
   <si>
+    <t>A subset of the SignBD-Word dataset utilizing 11 numeral Bengali digit signs composed of extracted RGB human body pose keypoints skeleton data</t>
+  </si>
+  <si>
     <t>Not explicitly stated (recent based on context).</t>
   </si>
   <si>
-    <t>A subset of the SignBD-Word dataset utilizing 11 numeral Bengali digit signs composed of extracted RGB human body pose keypoints skeleton data</t>
-  </si>
-  <si>
     <t xml:space="preserve"> A hybrid architecture combining 3DCNN and bidirectional LSTM (BiLSTM) layers, utilizing DenseNet-201 as a base feature extractor for classifying body joint skeleton motion patterns</t>
   </si>
   <si>
+    <t>Pioneered the implementation of DenseNet-201 combined with 3DCNN and BiLSTM for dynamic BdSL digit recognition based on skeleton motion patterns</t>
+  </si>
+  <si>
     <t xml:space="preserve"> The ensemble model (DenseNet-201+3DCNN+BiLSTM) achieved the highest scores (Precision 0.37, Recall 0.36, F1-Score 0.33), which increased accuracy by 4.54% compared to using DenseNet-201+BiLSTM alone</t>
   </si>
   <si>
-    <t>Pioneered the implementation of DenseNet-201 combined with 3DCNN and BiLSTM for dynamic BdSL digit recognition based on skeleton motion patterns</t>
-  </si>
-  <si>
     <t>IsharaNet: A robust nested feature fusion coupled with attention incorporated width scaled lightweight architecture for Bengali sign language recognition</t>
   </si>
   <si>
@@ -177,21 +201,6 @@
   </si>
   <si>
     <t>The Transformer model achieved 98.12% test accuracy, significantly outperforming baselines such as Sequential LSTM (81.21%) and SSD MobileNet V2 (78.02%)</t>
-  </si>
-  <si>
-    <t>BAUST Lipi, comprising 18,000 images covering 36 Bengali symbols (30 consonants and 6 vowels)</t>
-  </si>
-  <si>
-    <t>A hybrid Convolutional Neural Network (CNN) model integrated with multiple convolutional layers, dropout techniques, and LSTM layers</t>
-  </si>
-  <si>
-    <t>The proposed hybrid CNN-LSTM model achieved a testing accuracy rate of 97.28% (97.92% overall accuracy)</t>
-  </si>
-  <si>
-    <t>The study utilized YOLOv4 for real-time hand sign detection from full-frame images and tested multiple pre-trained deep learning models (Xception, InceptionV3, InceptionResNetv2, ResNet50V2, DenseNet) for cropped image recognition</t>
-  </si>
-  <si>
-    <t>The YOLOv11 model outperformed previous YOLO versions (v8, v9, v10, v12), achieving a precision of 99.12%, recall of 99.63%, and mAP of 99.4%</t>
   </si>
   <si>
     <t>s</t>
@@ -200,47 +209,204 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="13"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF303030"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF303030"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
-      <color rgb="FF303030"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -249,18 +415,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -268,42 +620,328 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -352,7 +990,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -385,26 +1023,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -437,23 +1058,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -615,130 +1219,145 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91718BDA-A7AF-4253-B864-230AF643558B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="34.7265625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.90625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="48.54296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="53.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="34.725" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.9083333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.54166666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="48.5416666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="53.5416666666667" style="1" customWidth="1"/>
     <col min="6" max="6" width="45" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="1"/>
+    <col min="7" max="16384" width="8.725" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="6" t="s">
+    <row r="1" ht="20.25" spans="1:6">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="66" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+    <row r="2" ht="105" customHeight="1" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1">
         <v>2024</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>49</v>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="99" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2">
+    <row r="8" ht="66" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2024</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="82.5" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3">
         <v>2023</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>11</v>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="99" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2">
+    <row r="10" ht="82.5" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="3">
         <v>2024</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>16</v>
+      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="115.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="2">
+    <row r="11" ht="99" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="3">
         <v>2025</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>51</v>
+      <c r="D11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -746,27 +1365,27 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+    <row r="13" ht="94.5" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -774,90 +1393,91 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+    <row r="15" ht="63" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1">
         <v>2025</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+    <row r="16" ht="78.75" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1">
         <v>2023</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="62" x14ac:dyDescent="0.35">
+    <row r="17" ht="63" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1">
         <v>2023</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="18" ht="63" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1">
         <v>2025</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/BdsL_paper_Summary.xlsx
+++ b/BdsL_paper_Summary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6780"/>
+    <workbookView windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>Paper Title</t>
   </si>
@@ -63,6 +63,95 @@
   <si>
     <t xml:space="preserve">Best Accuracy Achieved: 99.78% on the KU-BdSL dataset using GA-optimized KUNet.
 </t>
+  </si>
+  <si>
+    <t>Bangla Sign Language (BdSL) Alphabets and Numerals Classification Using a Deep Learning Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary Dataset: BdSL-D1500 [31] comprises with 132,061 images   with 87 classes   and                      Secondary Dataset: BdSLHD-2300 [34] (for hand segmentation) comprises with 2,300 images
+</t>
+  </si>
+  <si>
+    <t>Two main approaches were used:
+1.Classification with Background:-Used transfer learning on pre-trained CNNs: ResNet18, MobileNet_V2, and EfficientNet_B1 with Weights initialized from ImageNet; no layers frozen and Applied online data augmentation (rotation, flip, padding, resizing) 2.Classification without Background:-Train hand segmentation models on BdSLHD-2300 using DenseNet201-FPN, U-Net, and M-UNet and also Used CAM, Smoothed Grad-CAM++, and Score-CAM to interpret model decisions and verify focus on hand regions</t>
+  </si>
+  <si>
+    <t>Created and made publicly available the largest BdSL dataset (BdSL-D1500) with 87 classes and ~132,000 images, covering diverse backgrounds and skin tones and Developed a hand segmentation dataset (BdSLHD-2300) with 2,300 manually annotated images and also proposed and compared two pipelines: classification with and without background.</t>
+  </si>
+  <si>
+    <t>Best Model: ResNet18 (classification with background)
+Accuracy: 99.99%
+Precision: 99.99%                                         CAM, Grad-CAM++, and Score-CAM confirmed that models focused on hand regions, not backgrounds, for prediction.</t>
+  </si>
+  <si>
+    <t>Bengali-Sign: A Machine Learning-Based Bengali Sign Language Interpretation for Deaf and Non-Verbal People</t>
+  </si>
+  <si>
+    <t>KU-BdSL (Khulna University Bengali Sign Language Dataset)
+Total Images: 1,500 original samples ;Classes: 30 classes (Bengali alphabets); Participants: 33 participants (25 males, 8 females); Augmentation is applied to create a more robust dataset
+-Final Augmented Dataset Size: 15,000 samples</t>
+  </si>
+  <si>
+    <t>Model Architecture: CNN with Squeeze Excitation (SE) blocks; Data Preprocessing:
+Augmentation applied: random brightness (70% probability), RGB shift (shift limits: 5 for each channel, 70% probability), motion blur (blur limit: 7, 70% probability); Explainable AI (XAI): Used SHAP (SHapley Additive eXplanation) to interpret model decisions; Smartphone Application Development;
+Built using Flutter framework for cross-platform compatibility (Android, iOS, etc.)</t>
+  </si>
+  <si>
+    <t>Developed a CNN-SE network achieving 99.86% accuracy on KU-BdSL dataset, outperforming many existing models.
+First application of SHAP analysis in Bengali sign language recognition to interpret model decisions and confirm focus on hand regions.Created a fully functional smartphone application (KI-BdSL) to deploy the model for real-world use, enabling:
+Offline prediction, User-contributed data collection for continuous improvement,Cloud-based model updates.
+Demonstrated the importance of channel-wise attention (SE blocks) in improving sign language recognition performance.</t>
+  </si>
+  <si>
+    <t>Accuracy: 99.86% on test set.                          Real-World User Testing:                                 User 1: 80% accuracy (24/30 signs correctly predicted),User 2: 26.7% accuracy (8/30 signs correctly predicted).                                Smartphone Application:
+Successfully deployed and tested,
+Enables real-time and offline prediction,
+Allows user data donation for model improvement,
+Catalog feature supports self-learning of sign language</t>
+  </si>
+  <si>
+    <t>BdSL-SPOTER: A Transformer-Based
+Framework for Bengali Sign Language
+Recognition with Cultural Adaptation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BdSLW60 comprise with 9,307 videos and 60 sign classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model Architecture: BdSL-SPOTER (Sign POse-based TransformER adapted for Bengali Sign Language)
+Transformer Encoder: 4 layers (optimized for low-resource setting); Classification Head: 3 hidden layers with normalization, GELU activation, dropout, and softmax (60 classes)
+Preprocessing Pipeline:
+Pose extraction via MediaPipe Holistic
+BdSL-specific signing space normalization.  </t>
+  </si>
+  <si>
+    <t>First transformer-based architecture specifically tailored for Bengali Sign Language recognition with cultural adaptations and Introduced BdSL-specific preprocessing. Achieved state-of-the-art performance on BdSLW60 benchmark: 97.92% Top-1 accuracy (22.82% improvement over Bi-LSTM baseline)</t>
+  </si>
+  <si>
+    <t>Top-1 Accuracy: 97.92% (on BdSLW60 validation set) ,Top-5 Accuracy: 99.80%
+Macro F1 Score: 0.979</t>
+  </si>
+  <si>
+    <t>Sign Language Detection and Conversion to Readable Bengali
+Words using BdSL</t>
+  </si>
+  <si>
+    <t>Custom-collected BdSL dataset (no official name given in the document).Total Signs: 102 words (selected from over 600 crowd-sourced suggestions) and  Collaboration with a sign language specialist (Mukta) who demonstrated the signs</t>
+  </si>
+  <si>
+    <t>Data Collection &amp; Preprocessing:
+A website was created for the public to suggest commonly used words, resulting in over 600 suggestions.102 words were finalized with the help of a sign language specialist.30 photos per sign were taken, cropped, and scaled. Proposed Custom Model (LSTM with Mediapipe):
+Feature Extraction: Mediapipe handles the heavy lifting of extracting meaningful features from the images/video frames. Sequence Learning: A Long Short-Term Memory (LSTM) network is the core classifier. It takes the sequences of features extracted by Mediapipe as input. Other Models Tested (for Comparison):
+ResNet (Residual Network) and SSDMobileNet</t>
+  </si>
+  <si>
+    <t>This thesis makes several notable contributions to the field of Bengali Sign Language recognition:
+Expansion of BdSL Lexicon,Novel Dataset creation and effective real-time pipeline,Practical Application Development and Focus on Sentence-Level Translation</t>
+  </si>
+  <si>
+    <t>The proposed LSTM with Mediapipe model significantly outperformed the other models tested.
+Best Model Performance (LSTM with Mediapipe):
+Precision: 96.50%</t>
   </si>
   <si>
     <t>BAUST Lipi: A BdSL Dataset with Deep Learning Based Bangla Sign Language Recognition</t>
@@ -216,7 +305,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,13 +344,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -415,6 +497,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE4FE00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -554,12 +642,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -721,157 +803,160 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -880,7 +965,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -939,6 +1024,12 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="007F7F7F"/>
+      <color rgb="00E4FE00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1228,252 +1319,333 @@
   <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="34.725" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.9083333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.54166666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="48.5416666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="53.5416666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="45" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.725" style="1"/>
+    <col min="1" max="1" width="34.725" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.9083333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.54166666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="48.5416666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="53.5416666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="45" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.725" style="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" ht="105" customHeight="1" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>2024</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="3" ht="66" customHeight="1" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" ht="65" customHeight="1" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="68" customHeight="1" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="67" customHeight="1" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1"/>
     <row r="8" ht="66" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="A8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="5">
         <v>2024</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>15</v>
+      <c r="D8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="A9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="4">
         <v>2023</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>20</v>
+      <c r="D9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="82.5" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="A10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="4">
         <v>2024</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>25</v>
+      <c r="D10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="99" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="3">
+      <c r="A11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="4">
         <v>2025</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>30</v>
+      <c r="D11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" ht="94.5" spans="1:6">
-      <c r="A13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>36</v>
+      <c r="A13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" ht="63" spans="1:6">
-      <c r="A15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="1">
+      <c r="A15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="2">
         <v>2025</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>41</v>
+      <c r="D15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" ht="78.75" spans="1:6">
-      <c r="A16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="1">
+      <c r="A16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="2">
         <v>2023</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>46</v>
+      <c r="D16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="17" ht="63" spans="1:6">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="1">
+      <c r="A17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="2">
         <v>2023</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>51</v>
+      <c r="D17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="63" spans="1:9">
-      <c r="A18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="1">
+      <c r="A18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="2">
         <v>2025</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>57</v>
+      <c r="D18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
